--- a/data/detail.xlsx
+++ b/data/detail.xlsx
@@ -49,7 +49,7 @@
     <t>number_of_lines</t>
   </si>
   <si>
-    <t>numer_of_lines_under_construction</t>
+    <t>number_of_lines_under_construction</t>
   </si>
   <si>
     <t>number_of_stations</t>
@@ -676,7 +676,7 @@
     <t>65K</t>
   </si>
   <si>
-    <t>Hangzhou-Haikou Intercity Railway</t>
+    <t>Hangzhou-Haining Intercity Rail</t>
   </si>
   <si>
     <t>嘉兴（海宁）、杭州</t>
@@ -746,7 +746,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -775,6 +775,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1234,128 +1240,128 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1369,6 +1375,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3640,7 +3649,7 @@
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="5" t="s">
         <v>215</v>
       </c>
       <c r="C45" t="s">
